--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76618B3B-C65E-4127-B264-C72DFBE98BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7969AB50-00ED-47FD-8FDC-807AB4A55641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28590" yWindow="-6195" windowWidth="16410" windowHeight="11850" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
   <si>
     <t>Id</t>
   </si>
@@ -240,6 +240,30 @@
   </si>
   <si>
     <t>장비 선택 창 탭 버튼</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreviewPlayer</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_PREVIEW_PLAYER</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터 셋업레벨 프리뷰 캐릭터</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_PART_WEAPON</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 테스트 모델</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1192,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1326,6 +1350,34 @@
       </c>
       <c r="D9" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7969AB50-00ED-47FD-8FDC-807AB4A55641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D4F5E-A4AD-4D69-B437-9C8B2C5EC9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>Id</t>
   </si>
@@ -264,6 +264,18 @@
   </si>
   <si>
     <t>플레이어 테스트 모델</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>연출용 카메라</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_CAMERA_CINEMATIC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Camera_Cinematic</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1216,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1378,6 +1390,20 @@
       </c>
       <c r="D11" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7D4F5E-A4AD-4D69-B437-9C8B2C5EC9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B401CDF-3792-4D24-8982-3D430FA212DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="28680" yWindow="-165" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -276,6 +276,17 @@
   </si>
   <si>
     <t>Camera_Cinematic</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_WeaponType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_WEAPON_TYPE</t>
+  </si>
+  <si>
+    <t>플레이어 무기 텍스처</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1414,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA21448-B4F7-4911-8C4B-B5D5984DD267}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.75" customWidth="1"/>
@@ -1591,6 +1602,20 @@
         <v>62</v>
       </c>
     </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B401CDF-3792-4D24-8982-3D430FA212DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16766A04-3A1D-458E-97E2-4095540F87A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-165" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
-    <sheet name="UI" sheetId="2" r:id="rId2"/>
+    <sheet name="Skill" sheetId="3" r:id="rId2"/>
+    <sheet name="UI" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
   <si>
     <t>Id</t>
   </si>
@@ -287,6 +288,52 @@
   </si>
   <si>
     <t>플레이어 무기 텍스처</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Object</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_OBJECT</t>
+  </si>
+  <si>
+    <t>스킬 오브젝트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Projectile</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_PROJECTILE</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 프로젝타일 (투사체)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_RasenShuriken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_RASENSHURIKEN</t>
+  </si>
+  <si>
+    <t>나선 수리검</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rasengan</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_RASENGAN</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>나선환</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1424,6 +1471,93 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BF1AA5-CDB3-449D-AF4C-F0BA2E56147C}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA21448-B4F7-4911-8C4B-B5D5984DD267}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16766A04-3A1D-458E-97E2-4095540F87A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A695C27C-91D1-4F8C-8C3F-944847A70A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="90">
   <si>
     <t>Id</t>
   </si>
@@ -334,6 +334,18 @@
   </si>
   <si>
     <t>나선환</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_Announce</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>콤보 인덱스</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_ANNOUNCE_COMBO</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1559,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA21448-B4F7-4911-8C4B-B5D5984DD267}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.75" customWidth="1"/>
@@ -1750,6 +1762,20 @@
         <v>74</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A695C27C-91D1-4F8C-8C3F-944847A70A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51909933-A1D2-49CB-B5DF-7414770995A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="93">
   <si>
     <t>Id</t>
   </si>
@@ -346,6 +346,17 @@
   </si>
   <si>
     <t>OBJECT_TYPE_UI_ANNOUNCE_COMBO</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_Targeting</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_TARGETING</t>
+  </si>
+  <si>
+    <t>타겟팅 UI</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1571,7 +1582,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA21448-B4F7-4911-8C4B-B5D5984DD267}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.75" customWidth="1"/>
@@ -1776,6 +1787,20 @@
         <v>88</v>
       </c>
     </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51909933-A1D2-49CB-B5DF-7414770995A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3485736C-AEDE-4DAE-AD9B-5F8BEED11452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="5685" yWindow="1665" windowWidth="20700" windowHeight="11850" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
     <sheet name="Skill" sheetId="3" r:id="rId2"/>
-    <sheet name="UI" sheetId="2" r:id="rId3"/>
+    <sheet name="Monster" sheetId="4" r:id="rId3"/>
+    <sheet name="UI" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="96">
   <si>
     <t>Id</t>
   </si>
@@ -357,6 +358,18 @@
   </si>
   <si>
     <t>타겟팅 UI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 베이스 공격</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_Attack</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_MONSTER_ATTACK</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1581,6 +1594,50 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A02F8E6-3F9C-491F-97A8-09169CCDA713}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA21448-B4F7-4911-8C4B-B5D5984DD267}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3485736C-AEDE-4DAE-AD9B-5F8BEED11452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25F3FE1-040D-413F-904C-037D0223E364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="1665" windowWidth="20700" windowHeight="11850" activeTab="2" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="99">
   <si>
     <t>Id</t>
   </si>
@@ -370,6 +370,17 @@
   </si>
   <si>
     <t>OBJECT_TYPE_SKILL_MONSTER_ATTACK</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Particle_Instance</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_INSTANCED_PARTICLE_POINT</t>
+  </si>
+  <si>
+    <t>파티클 인스턴스</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1322,7 +1333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1498,6 +1509,20 @@
       </c>
       <c r="D12" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25F3FE1-040D-413F-904C-037D0223E364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B948D7E1-A364-4F47-88B3-8FBDF93939C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -381,6 +381,40 @@
   </si>
   <si>
     <t>파티클 인스턴스</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_FIREBALL</t>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_CHIDORI</t>
+  </si>
+  <si>
+    <t>Skill_FireBall</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Chidori</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>화둔 호화구</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>치도리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Mesh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_EFFECT_MESH</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이페펙트 메쉬</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1333,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1525,6 +1559,20 @@
         <v>98</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1533,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BF1AA5-CDB3-449D-AF4C-F0BA2E56147C}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -1610,6 +1658,34 @@
       </c>
       <c r="D5" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B948D7E1-A364-4F47-88B3-8FBDF93939C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CE19AD-70B6-4299-AF92-C7BE80609141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
   <si>
     <t>Id</t>
   </si>
@@ -414,7 +414,29 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>이페펙트 메쉬</t>
+    <t>Effect_Billboard</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_EFFECT_BILLBOARD</t>
+  </si>
+  <si>
+    <t>이펙트 메쉬</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이펙트 빌보드 되는거 2D</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attach_Effect</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_ATTACHED_EFFECT</t>
+  </si>
+  <si>
+    <t>플레이어한테 붙일 이팩?펙트</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1367,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1570,7 +1592,35 @@
         <v>45</v>
       </c>
       <c r="D14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CE19AD-70B6-4299-AF92-C7BE80609141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068F46F1-453B-4A2D-941D-52FA2B14B516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="117">
   <si>
     <t>Id</t>
   </si>
@@ -437,6 +437,17 @@
   </si>
   <si>
     <t>플레이어한테 붙일 이팩?펙트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_RasenShuriken_Hit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_RASENSHURIKEN_HIT</t>
+  </si>
+  <si>
+    <t>나선 수리검 터질때 분리</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1631,10 +1642,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BF1AA5-CDB3-449D-AF4C-F0BA2E56147C}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.75" customWidth="1"/>
+    <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="30.5" customWidth="1"/>
@@ -1736,6 +1747,20 @@
       </c>
       <c r="D7" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068F46F1-453B-4A2D-941D-52FA2B14B516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248F05DC-C116-4AEA-897F-532456745489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="120">
   <si>
     <t>Id</t>
   </si>
@@ -448,6 +448,17 @@
   </si>
   <si>
     <t>나선 수리검 터질때 분리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stretching_Effect</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_STRETCHING_MESH_EFFECT</t>
+  </si>
+  <si>
+    <t>스트레칭 메시</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1400,11 +1411,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
-    <col min="2" max="2" width="39.625" customWidth="1"/>
+    <col min="2" max="2" width="40.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="35.625" customWidth="1"/>
     <col min="5" max="5" width="43.5" customWidth="1"/>
@@ -1632,6 +1643,20 @@
       </c>
       <c r="D16" t="s">
         <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248F05DC-C116-4AEA-897F-532456745489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD2A8A2-FBFD-4785-921F-D6244B23561A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="126">
   <si>
     <t>Id</t>
   </si>
@@ -459,6 +459,28 @@
   </si>
   <si>
     <t>스트레칭 메시</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_RASENGAN_HIT</t>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_CHIDORI_HIT</t>
+  </si>
+  <si>
+    <t>치도리 히트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>나선환 히트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rasengan_Hit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Chidori_Hit</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1667,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BF1AA5-CDB3-449D-AF4C-F0BA2E56147C}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
@@ -1786,6 +1808,34 @@
       </c>
       <c r="D8" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD2A8A2-FBFD-4785-921F-D6244B23561A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253725BD-1F82-4C74-BECE-F1E122B7F162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="129">
   <si>
     <t>Id</t>
   </si>
@@ -481,6 +481,17 @@
   </si>
   <si>
     <t>Skill_Chidori_Hit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Proxy_Mesh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_COLLISION_PROXY</t>
+  </si>
+  <si>
+    <t>충돌용 메시</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1433,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1679,6 +1690,20 @@
       </c>
       <c r="D17" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253725BD-1F82-4C74-BECE-F1E122B7F162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF21D2-96DD-41C7-BB73-94D7839C1686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="141">
   <si>
     <t>Id</t>
   </si>
@@ -492,6 +492,53 @@
   </si>
   <si>
     <t>충돌용 메시</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_MonsterHp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 HP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_BossHp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_MultiplayerHp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스 HP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀티플레이어 HP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_MONSTER_HP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_BOSS_HP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_MULTIPLAYER_HP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkySphere</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKY_SPHERE</t>
+  </si>
+  <si>
+    <t>스카이 스피어</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1444,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1704,6 +1751,20 @@
       </c>
       <c r="D18" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1915,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA21448-B4F7-4911-8C4B-B5D5984DD267}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.75" customWidth="1"/>
@@ -2134,6 +2195,48 @@
         <v>92</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF21D2-96DD-41C7-BB73-94D7839C1686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED3493B-2488-419D-B65C-072620C5B804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="150">
   <si>
     <t>Id</t>
   </si>
@@ -539,6 +539,39 @@
   </si>
   <si>
     <t>스카이 스피어</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>WindmillShuriken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SHURIKEN</t>
+  </si>
+  <si>
+    <t>윈드밀 수리검</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_JINSUTANSU</t>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_KIRIN</t>
+  </si>
+  <si>
+    <t>진수천수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>기린</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Jinsutansu</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Kirin</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1491,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1767,6 +1800,20 @@
         <v>140</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1775,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BF1AA5-CDB3-449D-AF4C-F0BA2E56147C}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
@@ -1922,6 +1969,34 @@
       </c>
       <c r="D10" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED3493B-2488-419D-B65C-072620C5B804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BF9B21-8F69-4C34-9B16-974C8877936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="156">
   <si>
     <t>Id</t>
   </si>
@@ -553,9 +553,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>OBJECT_TYPE_JINSUTANSU</t>
-  </si>
-  <si>
     <t>OBJECT_TYPE_KIRIN</t>
   </si>
   <si>
@@ -567,11 +564,37 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Jinsutansu</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_Kirin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_ShinsuSenju</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SHINSUSENJU</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_ShinsuSenju_Arm</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SHINSUSENJU_ARM</t>
+  </si>
+  <si>
+    <t>진수천수 팔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Kirin_Hit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_KIRIN_HIT</t>
+  </si>
+  <si>
+    <t>기린 히트</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1822,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BF1AA5-CDB3-449D-AF4C-F0BA2E56147C}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
@@ -1976,27 +1999,55 @@
         <v>148</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BF9B21-8F69-4C34-9B16-974C8877936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0238DF-646A-4203-9E24-8EEF491B5B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -595,6 +595,29 @@
   </si>
   <si>
     <t>기린 히트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeshDebrisObject</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_MESH_DEBRIS</t>
+  </si>
+  <si>
+    <t>메시 파편</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss_Pain</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_BOSS_PAIN</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1547,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1835,6 +1858,34 @@
       </c>
       <c r="D20" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0238DF-646A-4203-9E24-8EEF491B5B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7172143-2068-495F-BC27-AE066FE4272B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="165">
   <si>
     <t>Id</t>
   </si>
@@ -618,6 +618,18 @@
   </si>
   <si>
     <t>보스</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_Trigger</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 스폰  트리거</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_WAVE_TRIGGER</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1570,7 +1582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1886,6 +1898,20 @@
       </c>
       <c r="D22" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7172143-2068-495F-BC27-AE066FE4272B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA8B683-26F4-438B-ADA1-1B3CC53EEC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA8B683-26F4-438B-ADA1-1B3CC53EEC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2DB428-3DB4-48E4-97A7-064532E8063D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="177">
   <si>
     <t>Id</t>
   </si>
@@ -630,6 +630,50 @@
   </si>
   <si>
     <t>OBJECT_TYPE_WAVE_TRIGGER</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChibakuTensei</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_CHIBAKU_TENSEI</t>
+  </si>
+  <si>
+    <t>지폭천성</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_Timer</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_TIMER</t>
+  </si>
+  <si>
+    <t>우측 상단 타이머</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_LockOn</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_LOCK_ON</t>
+  </si>
+  <si>
+    <t>와이어 락온 UI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>WireMesh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_WIRE_MESH_EFFECT</t>
+  </si>
+  <si>
+    <t>와이어</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1582,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1912,6 +1956,34 @@
       </c>
       <c r="D23" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2179,7 +2251,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA21448-B4F7-4911-8C4B-B5D5984DD267}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.75" customWidth="1"/>
@@ -2440,6 +2512,34 @@
         <v>134</v>
       </c>
     </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2DB428-3DB4-48E4-97A7-064532E8063D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A821A2A-E0DD-4240-92F4-57252B2712F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="183">
   <si>
     <t>Id</t>
   </si>
@@ -674,6 +674,28 @@
   </si>
   <si>
     <t>와이어</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mission_Marker</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_MISSION_MARKER</t>
+  </si>
+  <si>
+    <t>미션 마커</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Screen_Fade</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_UI_SCREEN_FADE</t>
+  </si>
+  <si>
+    <t>페이드 인&amp;아웃</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1626,7 +1648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -1984,6 +2006,34 @@
       </c>
       <c r="D25" t="s">
         <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_GameObject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A821A2A-E0DD-4240-92F4-57252B2712F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A07897-4A0D-4436-A684-17A33EA27F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F490CC2-A7D9-46CF-ADC0-DED084C63DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="198">
   <si>
     <t>Id</t>
   </si>
@@ -696,6 +696,62 @@
   </si>
   <si>
     <t>페이드 인&amp;아웃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_Leaf</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_MONSTER_LEAF</t>
+  </si>
+  <si>
+    <t>나뭇잎 닌자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster_Wood</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_MONSTER_WOOD</t>
+  </si>
+  <si>
+    <t>나무 소환 닌자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Part_Socket</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_PART_SOCKET</t>
+  </si>
+  <si>
+    <t>파츠 소켓</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_WoodHand</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_WOOD_HAND</t>
+  </si>
+  <si>
+    <t>우드핸드</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT_TYPE_SKILL_KAMUI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Kamui</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>카무이</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1648,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005A551A-B330-4316-9C70-6E9FEBBA1981}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -2036,6 +2092,48 @@
         <v>182</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
+        <v>191</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2044,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BF1AA5-CDB3-449D-AF4C-F0BA2E56147C}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.75" bestFit="1" customWidth="1"/>
@@ -2247,6 +2345,34 @@
       </c>
       <c r="D14" t="s">
         <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
